--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-labresult.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-labresult.xlsx
@@ -612,7 +612,7 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-labresult.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="433">
   <si>
     <t>Property</t>
   </si>
@@ -273,7 +273,7 @@
 【JP Core仕様】検体検査結果レポートのプロフィール</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -839,6 +839,15 @@
     <t>【JP Core仕様】レポートカテゴリーとして、LoincコードのLP29693-6(検体検査/LAB)を使用する。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP29693-6"/&gt;
+    &lt;display value="検体検査/LAB"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
@@ -860,16 +869,10 @@
     <t>DiagnosticReport.category:first.coding.system</t>
   </si>
   <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:first.coding.version</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.code</t>
-  </si>
-  <si>
-    <t>LP29693-6</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.display</t>
@@ -915,10 +918,6 @@
     <t>DiagnosticReport.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
     <t>DiagnosticReport.code.coding:laboratoryCode</t>
   </si>
   <si>
@@ -934,6 +933,13 @@
     <t>推奨コードは必須ではない、派生先によるコード体系を作成し割り振ることを否定しない</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_DocumentCodes_CS"/&gt;
+  &lt;code value="11502-2"/&gt;
+  &lt;display value="検体検査報告書"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>DiagnosticReport.code.coding:laboratoryCode.id</t>
   </si>
   <si>
@@ -958,9 +964,6 @@
     <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DocumentCodes_CS</t>
-  </si>
-  <si>
     <t>DiagnosticReport.code.coding:laboratoryCode.version</t>
   </si>
   <si>
@@ -979,9 +982,6 @@
     <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
-    <t>11502-2</t>
-  </si>
-  <si>
     <t>DiagnosticReport.code.coding:laboratoryCode.display</t>
   </si>
   <si>
@@ -992,9 +992,6 @@
   </si>
   <si>
     <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>検体検査報告書</t>
   </si>
   <si>
     <t>DiagnosticReport.code.coding:laboratoryCode.userSelected</t>
@@ -1053,7 +1050,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートが関係するヘルスケアイベントに関する情報</t>
+    <t>診断レポートが関係する診療イベントに関する情報</t>
   </si>
   <si>
     <t>【JP Core仕様】入院外来の区別や所在場所、担当診療科の情報に使用する。  
@@ -4660,7 +4657,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4679,7 +4676,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4726,7 +4723,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>193</v>
@@ -4838,7 +4835,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>199</v>
@@ -4952,7 +4949,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>204</v>
@@ -5068,7 +5065,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>213</v>
@@ -5180,7 +5177,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>214</v>
@@ -5294,7 +5291,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>215</v>
@@ -5339,7 +5336,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5567,7 +5564,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
@@ -5638,7 +5635,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>235</v>
@@ -5752,7 +5749,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>241</v>
@@ -5868,7 +5865,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>250</v>
@@ -5984,14 +5981,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6013,10 +6010,10 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6047,7 +6044,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6065,7 +6062,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -6080,24 +6077,24 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6206,10 +6203,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6320,10 +6317,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6395,7 +6392,7 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>287</v>
+        <v>188</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -6434,13 +6431,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>81</v>
@@ -6465,13 +6462,13 @@
         <v>205</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O42" t="s" s="2">
         <v>209</v>
@@ -6484,7 +6481,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -6552,10 +6549,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6664,10 +6661,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6778,10 +6775,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6789,7 +6786,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
@@ -6807,10 +6804,10 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>217</v>
@@ -6823,7 +6820,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>81</v>
@@ -6894,10 +6891,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7008,10 +7005,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7037,10 +7034,10 @@
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
@@ -7051,7 +7048,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>81</v>
@@ -7122,10 +7119,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7151,10 +7148,10 @@
         <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
@@ -7168,7 +7165,7 @@
         <v>81</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>81</v>
@@ -7236,10 +7233,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7352,10 +7349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7468,14 +7465,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7494,19 +7491,19 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O51" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7555,7 +7552,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7570,28 +7567,28 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7610,19 +7607,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7671,7 +7668,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7686,28 +7683,28 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7726,19 +7723,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7787,7 +7784,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7802,28 +7799,28 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7842,19 +7839,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7903,7 +7900,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7921,25 +7918,25 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7958,19 +7955,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8019,7 +8016,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8034,28 +8031,28 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8074,19 +8071,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8135,7 +8132,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8150,24 +8147,24 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8190,19 +8187,19 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8251,7 +8248,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8269,10 +8266,10 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8280,14 +8277,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8306,19 +8303,19 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O58" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8367,7 +8364,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8385,10 +8382,10 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8396,10 +8393,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8422,16 +8419,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8481,7 +8478,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8502,7 +8499,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8510,14 +8507,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8536,19 +8533,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8597,7 +8594,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8615,10 +8612,10 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -8626,10 +8623,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8738,10 +8735,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8852,14 +8849,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8881,10 +8878,10 @@
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -8939,7 +8936,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8968,10 +8965,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8997,16 +8994,16 @@
         <v>194</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9055,7 +9052,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9076,7 +9073,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9084,10 +9081,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9110,16 +9107,16 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9169,7 +9166,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -9190,7 +9187,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9198,14 +9195,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9227,16 +9224,16 @@
         <v>194</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9285,7 +9282,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9303,10 +9300,10 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9314,10 +9311,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9343,13 +9340,13 @@
         <v>182</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9378,10 +9375,10 @@
         <v>185</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9399,7 +9396,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9417,10 +9414,10 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -9428,10 +9425,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9454,19 +9451,19 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9515,7 +9512,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9533,10 +9530,10 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
